--- a/tracking_forms/037_pet_eye_contact_observation_log--tracking_forms.xlsx
+++ b/tracking_forms/037_pet_eye_contact_observation_log--tracking_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -757,8 +757,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
-    <col width="37" customWidth="1" min="2" max="2"/>
-    <col width="37" customWidth="1" min="3" max="3"/>
+    <col width="24" customWidth="1" min="2" max="2"/>
+    <col width="24" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -786,12 +786,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'label':_'normal'}</t>
+          <t>normal</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'label': 'Normal'}</t>
+          <t>Normal</t>
         </is>
       </c>
     </row>
@@ -803,12 +803,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'label':_'redness'}</t>
+          <t>redness</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'label': 'Redness'}</t>
+          <t>Redness</t>
         </is>
       </c>
     </row>
@@ -820,12 +820,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'label':_'discharge'}</t>
+          <t>discharge</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'label': 'Discharge'}</t>
+          <t>Discharge</t>
         </is>
       </c>
     </row>
@@ -837,12 +837,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'label':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'label': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -854,12 +854,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'label':_'n/a'}</t>
+          <t>n/a</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'label': 'N/A'}</t>
+          <t>N/A</t>
         </is>
       </c>
     </row>
@@ -871,12 +871,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'label':_'direct'}</t>
+          <t>direct</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'label': 'Direct'}</t>
+          <t>Direct</t>
         </is>
       </c>
     </row>
@@ -888,12 +888,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'label':_'indirect'}</t>
+          <t>indirect</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'label': 'Indirect'}</t>
+          <t>Indirect</t>
         </is>
       </c>
     </row>
@@ -905,12 +905,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'label':_'both'}</t>
+          <t>both</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'label': 'Both'}</t>
+          <t>Both</t>
         </is>
       </c>
     </row>
@@ -922,12 +922,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'label':_'n/a'}</t>
+          <t>n/a</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'label': 'N/A'}</t>
+          <t>N/A</t>
         </is>
       </c>
     </row>
@@ -939,12 +939,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'label':_'very_comfortable'}</t>
+          <t>very_comfortable</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'label': 'Very Comfortable'}</t>
+          <t>Very Comfortable</t>
         </is>
       </c>
     </row>
@@ -956,12 +956,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'label':_'somewhat_comfortable'}</t>
+          <t>somewhat_comfortable</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'label': 'Somewhat Comfortable'}</t>
+          <t>Somewhat Comfortable</t>
         </is>
       </c>
     </row>
@@ -973,12 +973,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'label':_'neutral'}</t>
+          <t>neutral</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'label': 'Neutral'}</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -990,12 +990,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'label':_'somewhat_uncomfortable'}</t>
+          <t>somewhat_uncomfortable</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'label': 'Somewhat Uncomfortable'}</t>
+          <t>Somewhat Uncomfortable</t>
         </is>
       </c>
     </row>
@@ -1007,12 +1007,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'label':_'very_uncomfortable'}</t>
+          <t>very_uncomfortable</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'label': 'Very Uncomfortable'}</t>
+          <t>Very Uncomfortable</t>
         </is>
       </c>
     </row>
@@ -1024,12 +1024,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'label':_'n/a'}</t>
+          <t>n/a</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'label': 'N/A'}</t>
+          <t>N/A</t>
         </is>
       </c>
     </row>
@@ -1041,12 +1041,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'label':_'improved'}</t>
+          <t>improved</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'label': 'Improved'}</t>
+          <t>Improved</t>
         </is>
       </c>
     </row>
@@ -1058,12 +1058,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'label':_'no_change'}</t>
+          <t>no_change</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'label': 'No Change'}</t>
+          <t>No Change</t>
         </is>
       </c>
     </row>
@@ -1075,12 +1075,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'label':_'worsened'}</t>
+          <t>worsened</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'label': 'Worsened'}</t>
+          <t>Worsened</t>
         </is>
       </c>
     </row>
@@ -1092,12 +1092,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'label':_'n/a'}</t>
+          <t>n/a</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'label': 'N/A'}</t>
+          <t>N/A</t>
         </is>
       </c>
     </row>
